--- a/prototype/sample-quote-guangdong.xlsx
+++ b/prototype/sample-quote-guangdong.xlsx
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-1332</t>
+    <t>报价编号：BJ-20260910-7965</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -284,7 +284,7 @@
     <t>需方签字（盖章）：____________________</t>
   </si>
   <si>
-    <t>计算明细 · BJ-20260910-1332</t>
+    <t>计算明细 · BJ-20260910-7965</t>
   </si>
   <si>
     <t>广州本地客户　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省内（免运费）</t>
@@ -1762,7 +1762,7 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-1332</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-7965</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/prototype/sample-quote-guangdong.xlsx
+++ b/prototype/sample-quote-guangdong.xlsx
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-7965</t>
+    <t>报价编号：BJ-20260910-6059</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -284,7 +284,7 @@
     <t>需方签字（盖章）：____________________</t>
   </si>
   <si>
-    <t>计算明细 · BJ-20260910-7965</t>
+    <t>计算明细 · BJ-20260910-6059</t>
   </si>
   <si>
     <t>广州本地客户　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省内（免运费）</t>
@@ -1762,7 +1762,7 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-7965</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-6059</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/prototype/sample-quote-guangdong.xlsx
+++ b/prototype/sample-quote-guangdong.xlsx
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-6059</t>
+    <t>报价编号：BJ-20260910-6838</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -284,7 +284,7 @@
     <t>需方签字（盖章）：____________________</t>
   </si>
   <si>
-    <t>计算明细 · BJ-20260910-6059</t>
+    <t>计算明细 · BJ-20260910-6838</t>
   </si>
   <si>
     <t>广州本地客户　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省内（免运费）</t>
@@ -1762,7 +1762,7 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-6059</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-6838</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/prototype/sample-quote-guangdong.xlsx
+++ b/prototype/sample-quote-guangdong.xlsx
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-6838</t>
+    <t>报价编号：BJ-20260910-8390</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -284,7 +284,7 @@
     <t>需方签字（盖章）：____________________</t>
   </si>
   <si>
-    <t>计算明细 · BJ-20260910-6838</t>
+    <t>计算明细 · BJ-20260910-8390</t>
   </si>
   <si>
     <t>广州本地客户　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省内（免运费）</t>
@@ -1762,7 +1762,7 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-6838</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-8390</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/prototype/sample-quote-guangdong.xlsx
+++ b/prototype/sample-quote-guangdong.xlsx
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-8390</t>
+    <t>报价编号：BJ-20260910-5047</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -284,7 +284,7 @@
     <t>需方签字（盖章）：____________________</t>
   </si>
   <si>
-    <t>计算明细 · BJ-20260910-8390</t>
+    <t>计算明细 · BJ-20260910-5047</t>
   </si>
   <si>
     <t>广州本地客户　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省内（免运费）</t>
@@ -1762,7 +1762,7 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-8390</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-5047</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/prototype/sample-quote-guangdong.xlsx
+++ b/prototype/sample-quote-guangdong.xlsx
@@ -23,7 +23,7 @@
     <t>模  具  报  价  单</t>
   </si>
   <si>
-    <t>报价编号：BJ-20260910-5047</t>
+    <t>报价编号：BJ-20260910-3097</t>
   </si>
   <si>
     <t>报价日期：2026-09-10　有效期：2026-10-10</t>
@@ -119,46 +119,46 @@
     <t>5000 件</t>
   </si>
   <si>
+    <t>模具重量</t>
+  </si>
+  <si>
+    <t>800 kg</t>
+  </si>
+  <si>
+    <t>运输箱长</t>
+  </si>
+  <si>
+    <t>120 cm</t>
+  </si>
+  <si>
+    <t>运输箱宽</t>
+  </si>
+  <si>
+    <t>100 cm</t>
+  </si>
+  <si>
+    <t>运输箱高</t>
+  </si>
+  <si>
+    <t>80 cm</t>
+  </si>
+  <si>
+    <t>运费单价</t>
+  </si>
+  <si>
+    <t>1.2 元/kg</t>
+  </si>
+  <si>
+    <t>运输区域</t>
+  </si>
+  <si>
+    <t>广东省内（免运费）</t>
+  </si>
+  <si>
     <t>首单数量</t>
   </si>
   <si>
-    <t>300000 件</t>
-  </si>
-  <si>
-    <t>模具重量</t>
-  </si>
-  <si>
-    <t>800 kg</t>
-  </si>
-  <si>
-    <t>运输箱长</t>
-  </si>
-  <si>
-    <t>120 cm</t>
-  </si>
-  <si>
-    <t>运输箱宽</t>
-  </si>
-  <si>
-    <t>100 cm</t>
-  </si>
-  <si>
-    <t>运输箱高</t>
-  </si>
-  <si>
-    <t>80 cm</t>
-  </si>
-  <si>
-    <t>运费单价</t>
-  </si>
-  <si>
-    <t>1.2 元/kg</t>
-  </si>
-  <si>
-    <t>运输区域</t>
-  </si>
-  <si>
-    <t>广东省内（免运费）</t>
+    <t>300000</t>
   </si>
   <si>
     <t>二、费用明细</t>
@@ -284,10 +284,10 @@
     <t>需方签字（盖章）：____________________</t>
   </si>
   <si>
-    <t>计算明细 · BJ-20260910-5047</t>
-  </si>
-  <si>
-    <t>广州本地客户　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　首单数量：300000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省内（免运费）</t>
+    <t>计算明细 · BJ-20260910-3097</t>
+  </si>
+  <si>
+    <t>广州本地客户　·　产品名称：洗衣机控制面板　·　腔数：2 穴　·　单件重量：0.18 kg　·　模芯长：500 mm　·　模芯宽：400 mm　·　模芯高：150 mm　·　钢材单价：25 元/kg　·　钢材密度：7.85 g/cm³　·　原料单价：12 元/kg　·　注塑数量：5000 件　·　模具重量：800 kg　·　运输箱长：120 cm　·　运输箱宽：100 cm　·　运输箱高：80 cm　·　运费单价：1.2 元/kg　·　运输区域：广东省内（免运费）　·　首单数量：300000</t>
   </si>
   <si>
     <t>计算方式与代入过程</t>
@@ -1762,7 +1762,7 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-5047</oddFooter>
+    <oddFooter>&amp;L模具注塑报价系统&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;RBJ-20260910-3097</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
